--- a/informes_data/Primera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486432_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Primera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486432_PROCESSED_CHRONO.xlsx
@@ -565,10 +565,10 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>16.1635</v>
+        <v>15.9905</v>
       </c>
       <c r="E2" t="n">
-        <v>11.5989</v>
+        <v>11.4259</v>
       </c>
       <c r="F2" t="n">
         <v>4.5646</v>
@@ -610,10 +610,10 @@
         <v>2.8276</v>
       </c>
       <c r="S2" t="n">
-        <v>2.0381</v>
+        <v>1.865</v>
       </c>
       <c r="T2" t="n">
-        <v>0.9097</v>
+        <v>0.7367</v>
       </c>
       <c r="U2" t="n">
         <v>1.1284</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>3.6629</v>
+        <v>4.2675</v>
       </c>
       <c r="E3" t="n">
-        <v>0.3115</v>
+        <v>1.101</v>
       </c>
       <c r="F3" t="n">
-        <v>3.3514</v>
+        <v>3.1665</v>
       </c>
       <c r="G3" t="n">
         <v>0.9364</v>
@@ -688,13 +688,13 @@
         <v>1.9576</v>
       </c>
       <c r="S3" t="n">
-        <v>0.5737</v>
+        <v>1.1783</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.6609</v>
+        <v>0.1286</v>
       </c>
       <c r="U3" t="n">
-        <v>1.2346</v>
+        <v>1.0497</v>
       </c>
       <c r="V3" t="n">
         <v>0.1952</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>3.4227</v>
+        <v>3.4355</v>
       </c>
       <c r="E4" t="n">
-        <v>2.6259</v>
+        <v>2.6079</v>
       </c>
       <c r="F4" t="n">
-        <v>0.7967</v>
+        <v>0.8276</v>
       </c>
       <c r="G4" t="n">
         <v>0.5728</v>
@@ -766,13 +766,13 @@
         <v>1.5225</v>
       </c>
       <c r="S4" t="n">
-        <v>1.1321</v>
+        <v>1.1449</v>
       </c>
       <c r="T4" t="n">
-        <v>0.3581</v>
+        <v>0.3401</v>
       </c>
       <c r="U4" t="n">
-        <v>0.774</v>
+        <v>0.8048</v>
       </c>
       <c r="V4" t="n">
         <v>0.1952</v>
@@ -787,7 +787,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>D. KRAVIC</t>
+          <t>S. QUINTELA SALVADOR</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,58 +799,58 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>1.4525</v>
+        <v>2.28</v>
       </c>
       <c r="E5" t="n">
-        <v>-2.5113</v>
+        <v>-0.6829</v>
       </c>
       <c r="F5" t="n">
-        <v>3.9638</v>
+        <v>2.9629</v>
       </c>
       <c r="G5" t="n">
-        <v>-2.2777</v>
+        <v>0.4543</v>
       </c>
       <c r="H5" t="n">
-        <v>-4.2148</v>
+        <v>0.0152</v>
       </c>
       <c r="I5" t="n">
-        <v>1.9371</v>
+        <v>0.4391</v>
       </c>
       <c r="J5" t="n">
-        <v>-2.9174</v>
+        <v>0.413</v>
       </c>
       <c r="K5" t="n">
-        <v>-3.6824</v>
+        <v>1.0616</v>
       </c>
       <c r="L5" t="n">
-        <v>0.765</v>
+        <v>-0.6486</v>
       </c>
       <c r="M5" t="n">
-        <v>0.6398</v>
+        <v>0.0413</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.5324</v>
+        <v>-1.0464</v>
       </c>
       <c r="O5" t="n">
-        <v>1.1722</v>
+        <v>1.0877</v>
       </c>
       <c r="P5" t="n">
-        <v>1.7401</v>
+        <v>0.87</v>
       </c>
       <c r="Q5" t="n">
-        <v>-0.2175</v>
+        <v>-1.0875</v>
       </c>
       <c r="R5" t="n">
         <v>1.9576</v>
       </c>
       <c r="S5" t="n">
-        <v>1.9901</v>
+        <v>0.9556</v>
       </c>
       <c r="T5" t="n">
-        <v>0.6237</v>
+        <v>-0.008399999999999999</v>
       </c>
       <c r="U5" t="n">
-        <v>1.3664</v>
+        <v>0.9641</v>
       </c>
       <c r="V5" t="n">
         <v>0</v>
@@ -865,7 +865,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>S. QUINTELA SALVADOR</t>
+          <t>T. MUNNINGS</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,58 +877,58 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>1.2199</v>
+        <v>1.2797</v>
       </c>
       <c r="E6" t="n">
-        <v>-1.4039</v>
+        <v>0.3284</v>
       </c>
       <c r="F6" t="n">
-        <v>2.6238</v>
+        <v>0.9513</v>
       </c>
       <c r="G6" t="n">
-        <v>0.4543</v>
+        <v>0.3421</v>
       </c>
       <c r="H6" t="n">
-        <v>0.0152</v>
+        <v>-1.0675</v>
       </c>
       <c r="I6" t="n">
-        <v>0.4391</v>
+        <v>1.4096</v>
       </c>
       <c r="J6" t="n">
-        <v>0.413</v>
+        <v>0.6649</v>
       </c>
       <c r="K6" t="n">
-        <v>1.0616</v>
+        <v>-0.6356000000000001</v>
       </c>
       <c r="L6" t="n">
-        <v>-0.6486</v>
+        <v>1.3005</v>
       </c>
       <c r="M6" t="n">
-        <v>0.0413</v>
+        <v>-0.3228</v>
       </c>
       <c r="N6" t="n">
-        <v>-1.0464</v>
+        <v>-0.432</v>
       </c>
       <c r="O6" t="n">
-        <v>1.0877</v>
+        <v>0.1091</v>
       </c>
       <c r="P6" t="n">
+        <v>0.6525</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>-0.2175</v>
+      </c>
+      <c r="R6" t="n">
         <v>0.87</v>
       </c>
-      <c r="Q6" t="n">
-        <v>-1.0875</v>
-      </c>
-      <c r="R6" t="n">
-        <v>1.9576</v>
-      </c>
       <c r="S6" t="n">
-        <v>-0.1044</v>
+        <v>0.2851</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.7294</v>
+        <v>-0.119</v>
       </c>
       <c r="U6" t="n">
-        <v>0.625</v>
+        <v>0.4041</v>
       </c>
       <c r="V6" t="n">
         <v>0</v>
@@ -943,7 +943,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>F. DOS ANJOS DE PAULA</t>
+          <t>D. KRAVIC</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>0.9852</v>
+        <v>0.9155</v>
       </c>
       <c r="E7" t="n">
-        <v>4.5336</v>
+        <v>-2.7708</v>
       </c>
       <c r="F7" t="n">
-        <v>-3.5484</v>
+        <v>3.6863</v>
       </c>
       <c r="G7" t="n">
-        <v>-1.7016</v>
+        <v>-2.2777</v>
       </c>
       <c r="H7" t="n">
-        <v>0.2587</v>
+        <v>-4.2148</v>
       </c>
       <c r="I7" t="n">
-        <v>-1.9603</v>
+        <v>1.9371</v>
       </c>
       <c r="J7" t="n">
-        <v>1.9975</v>
+        <v>-2.9174</v>
       </c>
       <c r="K7" t="n">
-        <v>1.156</v>
+        <v>-3.6824</v>
       </c>
       <c r="L7" t="n">
-        <v>0.8415</v>
+        <v>0.765</v>
       </c>
       <c r="M7" t="n">
-        <v>-3.6992</v>
+        <v>0.6398</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.8974</v>
+        <v>-0.5324</v>
       </c>
       <c r="O7" t="n">
-        <v>-2.8018</v>
+        <v>1.1722</v>
       </c>
       <c r="P7" t="n">
+        <v>1.7401</v>
+      </c>
+      <c r="Q7" t="n">
         <v>-0.2175</v>
       </c>
-      <c r="Q7" t="n">
-        <v>-1.0875</v>
-      </c>
       <c r="R7" t="n">
-        <v>0.87</v>
+        <v>1.9576</v>
       </c>
       <c r="S7" t="n">
-        <v>1.497</v>
+        <v>1.4531</v>
       </c>
       <c r="T7" t="n">
-        <v>1.5382</v>
+        <v>0.3641</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.0412</v>
+        <v>1.089</v>
       </c>
       <c r="V7" t="n">
-        <v>1.4074</v>
+        <v>0</v>
       </c>
       <c r="W7" t="n">
-        <v>2.0854</v>
+        <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>-0.678</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>T. MUNNINGS</t>
+          <t>F. DOS ANJOS DE PAULA</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1033,73 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>0.8816000000000001</v>
+        <v>0.8225</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.1006</v>
+        <v>4.155</v>
       </c>
       <c r="F8" t="n">
-        <v>0.9821</v>
+        <v>-3.3326</v>
       </c>
       <c r="G8" t="n">
-        <v>0.3421</v>
+        <v>-1.7016</v>
       </c>
       <c r="H8" t="n">
-        <v>-1.0675</v>
+        <v>0.2587</v>
       </c>
       <c r="I8" t="n">
-        <v>1.4096</v>
+        <v>-1.9603</v>
       </c>
       <c r="J8" t="n">
-        <v>0.6649</v>
+        <v>1.9975</v>
       </c>
       <c r="K8" t="n">
-        <v>-0.6356000000000001</v>
+        <v>1.156</v>
       </c>
       <c r="L8" t="n">
-        <v>1.3005</v>
+        <v>0.8415</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.3228</v>
+        <v>-3.6992</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.432</v>
+        <v>-0.8974</v>
       </c>
       <c r="O8" t="n">
-        <v>0.1091</v>
+        <v>-2.8018</v>
       </c>
       <c r="P8" t="n">
-        <v>0.6525</v>
+        <v>-0.2175</v>
       </c>
       <c r="Q8" t="n">
-        <v>-0.2175</v>
+        <v>-1.0875</v>
       </c>
       <c r="R8" t="n">
         <v>0.87</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.1131</v>
+        <v>1.3342</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.548</v>
+        <v>1.1596</v>
       </c>
       <c r="U8" t="n">
-        <v>0.4349</v>
+        <v>0.1745</v>
       </c>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>1.4074</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>2.0854</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>-0.678</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Y. BARRUETA</t>
+          <t>A. GALAN POZO</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,73 +1111,73 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.869</v>
+        <v>-0.868</v>
       </c>
       <c r="E9" t="n">
-        <v>1.2775</v>
+        <v>1.1746</v>
       </c>
       <c r="F9" t="n">
-        <v>-2.1465</v>
+        <v>-2.0426</v>
       </c>
       <c r="G9" t="n">
-        <v>-3.0916</v>
+        <v>-3.2353</v>
       </c>
       <c r="H9" t="n">
-        <v>-0.4197</v>
+        <v>-0.9125</v>
       </c>
       <c r="I9" t="n">
-        <v>-2.6719</v>
+        <v>-2.3229</v>
       </c>
       <c r="J9" t="n">
-        <v>-0.6403</v>
+        <v>0.0813</v>
       </c>
       <c r="K9" t="n">
-        <v>-0.0698</v>
+        <v>-0.0151</v>
       </c>
       <c r="L9" t="n">
-        <v>-0.5705</v>
+        <v>0.0964</v>
       </c>
       <c r="M9" t="n">
-        <v>-2.4512</v>
+        <v>-3.3167</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.3499</v>
+        <v>-0.8974</v>
       </c>
       <c r="O9" t="n">
-        <v>-2.1013</v>
+        <v>-2.4193</v>
       </c>
       <c r="P9" t="n">
-        <v>-0.6525</v>
+        <v>-0.2175</v>
       </c>
       <c r="Q9" t="n">
-        <v>-1.305</v>
+        <v>-1.0875</v>
       </c>
       <c r="R9" t="n">
-        <v>0.6525</v>
+        <v>0.87</v>
       </c>
       <c r="S9" t="n">
-        <v>1.2931</v>
+        <v>1.3726</v>
       </c>
       <c r="T9" t="n">
-        <v>1.3327</v>
+        <v>0.8556</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.0395</v>
+        <v>0.517</v>
       </c>
       <c r="V9" t="n">
-        <v>1.582</v>
+        <v>1.2122</v>
       </c>
       <c r="W9" t="n">
-        <v>1.8902</v>
+        <v>1.3252</v>
       </c>
       <c r="X9" t="n">
-        <v>-0.3082</v>
+        <v>-0.113</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>A. GALAN POZO</t>
+          <t>A. BARCELLO</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,73 +1189,73 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-1.2748</v>
+        <v>-1.0273</v>
       </c>
       <c r="E10" t="n">
-        <v>0.3671</v>
+        <v>2.4216</v>
       </c>
       <c r="F10" t="n">
-        <v>-1.6419</v>
+        <v>-3.4489</v>
       </c>
       <c r="G10" t="n">
-        <v>-3.2353</v>
+        <v>-3.7076</v>
       </c>
       <c r="H10" t="n">
-        <v>-0.9125</v>
+        <v>-0.0333</v>
       </c>
       <c r="I10" t="n">
-        <v>-2.3229</v>
+        <v>-3.6743</v>
       </c>
       <c r="J10" t="n">
-        <v>0.0813</v>
+        <v>-0.7894</v>
       </c>
       <c r="K10" t="n">
-        <v>-0.0151</v>
+        <v>0.3166</v>
       </c>
       <c r="L10" t="n">
-        <v>0.0964</v>
+        <v>-1.106</v>
       </c>
       <c r="M10" t="n">
-        <v>-3.3167</v>
+        <v>-2.9182</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.8974</v>
+        <v>-0.3499</v>
       </c>
       <c r="O10" t="n">
-        <v>-2.4193</v>
+        <v>-2.5683</v>
       </c>
       <c r="P10" t="n">
+        <v>0.435</v>
+      </c>
+      <c r="Q10" t="n">
         <v>-0.2175</v>
       </c>
-      <c r="Q10" t="n">
-        <v>-1.0875</v>
-      </c>
       <c r="R10" t="n">
-        <v>0.87</v>
+        <v>0.6525</v>
       </c>
       <c r="S10" t="n">
-        <v>0.9658</v>
+        <v>1.0332</v>
       </c>
       <c r="T10" t="n">
-        <v>0.0481</v>
+        <v>0.9734</v>
       </c>
       <c r="U10" t="n">
-        <v>0.9177</v>
+        <v>0.0598</v>
       </c>
       <c r="V10" t="n">
         <v>1.2122</v>
       </c>
       <c r="W10" t="n">
-        <v>1.3252</v>
+        <v>2.4552</v>
       </c>
       <c r="X10" t="n">
-        <v>-0.113</v>
+        <v>-1.243</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>A. BARCELLO</t>
+          <t>Y. BARRUETA</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,67 +1267,67 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-1.3068</v>
+        <v>-1.26</v>
       </c>
       <c r="E11" t="n">
-        <v>2.1729</v>
+        <v>0.8557</v>
       </c>
       <c r="F11" t="n">
-        <v>-3.4797</v>
+        <v>-2.1157</v>
       </c>
       <c r="G11" t="n">
-        <v>-3.7076</v>
+        <v>-3.0916</v>
       </c>
       <c r="H11" t="n">
-        <v>-0.0333</v>
+        <v>-0.4197</v>
       </c>
       <c r="I11" t="n">
-        <v>-3.6743</v>
+        <v>-2.6719</v>
       </c>
       <c r="J11" t="n">
-        <v>-0.7894</v>
+        <v>-0.6403</v>
       </c>
       <c r="K11" t="n">
-        <v>0.3166</v>
+        <v>-0.0698</v>
       </c>
       <c r="L11" t="n">
-        <v>-1.106</v>
+        <v>-0.5705</v>
       </c>
       <c r="M11" t="n">
-        <v>-2.9182</v>
+        <v>-2.4512</v>
       </c>
       <c r="N11" t="n">
         <v>-0.3499</v>
       </c>
       <c r="O11" t="n">
-        <v>-2.5683</v>
+        <v>-2.1013</v>
       </c>
       <c r="P11" t="n">
-        <v>0.435</v>
+        <v>-0.6525</v>
       </c>
       <c r="Q11" t="n">
-        <v>-0.2175</v>
+        <v>-1.305</v>
       </c>
       <c r="R11" t="n">
         <v>0.6525</v>
       </c>
       <c r="S11" t="n">
-        <v>0.7536</v>
+        <v>0.9022</v>
       </c>
       <c r="T11" t="n">
-        <v>0.7246</v>
+        <v>0.9109</v>
       </c>
       <c r="U11" t="n">
-        <v>0.029</v>
+        <v>-0.008699999999999999</v>
       </c>
       <c r="V11" t="n">
-        <v>1.2122</v>
+        <v>1.582</v>
       </c>
       <c r="W11" t="n">
-        <v>2.4552</v>
+        <v>1.8902</v>
       </c>
       <c r="X11" t="n">
-        <v>-1.243</v>
+        <v>-0.3082</v>
       </c>
     </row>
     <row r="12">
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-9.9734</v>
+        <v>-9.074299999999999</v>
       </c>
       <c r="E12" t="n">
-        <v>-3.8243</v>
+        <v>-3.1718</v>
       </c>
       <c r="F12" t="n">
-        <v>-6.1491</v>
+        <v>-5.9025</v>
       </c>
       <c r="G12" t="n">
         <v>-5.2523</v>
@@ -1390,13 +1390,13 @@
         <v>0</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.5206</v>
+        <v>0.3785</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.2379</v>
+        <v>0.4146</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.2826</v>
+        <v>-0.0361</v>
       </c>
       <c r="V12" t="n">
         <v>-1.808</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>14.3643</v>
+        <v>16.7616</v>
       </c>
       <c r="E13" t="n">
-        <v>15.0473</v>
+        <v>17.4446</v>
       </c>
       <c r="F13" t="n">
-        <v>-0.6831999999999985</v>
+        <v>-0.6831000000000014</v>
       </c>
       <c r="G13" t="n">
         <v>-4.812799999999999</v>
@@ -1438,13 +1438,13 @@
         <v>-3.223</v>
       </c>
       <c r="I13" t="n">
-        <v>-1.589899999999999</v>
+        <v>-1.5899</v>
       </c>
       <c r="J13" t="n">
         <v>10.4843</v>
       </c>
       <c r="K13" t="n">
-        <v>3.9258</v>
+        <v>3.925800000000001</v>
       </c>
       <c r="L13" t="n">
         <v>6.558399999999999</v>
@@ -1453,13 +1453,13 @@
         <v>-15.2971</v>
       </c>
       <c r="N13" t="n">
-        <v>-7.149</v>
+        <v>-7.148999999999999</v>
       </c>
       <c r="O13" t="n">
-        <v>-8.148100000000001</v>
+        <v>-8.148099999999999</v>
       </c>
       <c r="P13" t="n">
-        <v>4.350099999999999</v>
+        <v>4.3501</v>
       </c>
       <c r="Q13" t="n">
         <v>-9.787700000000001</v>
@@ -1468,13 +1468,13 @@
         <v>14.1379</v>
       </c>
       <c r="S13" t="n">
-        <v>9.5054</v>
+        <v>11.9027</v>
       </c>
       <c r="T13" t="n">
-        <v>3.358899999999999</v>
+        <v>5.7562</v>
       </c>
       <c r="U13" t="n">
-        <v>6.146699999999999</v>
+        <v>6.1466</v>
       </c>
       <c r="V13" t="n">
         <v>5.321400000000001</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>3.4935</v>
+        <v>4.439</v>
       </c>
       <c r="E14" t="n">
-        <v>2.3554</v>
+        <v>2.8025</v>
       </c>
       <c r="F14" t="n">
-        <v>1.1381</v>
+        <v>1.6366</v>
       </c>
       <c r="G14" t="n">
         <v>3.4902</v>
@@ -1546,13 +1546,13 @@
         <v>1.0875</v>
       </c>
       <c r="S14" t="n">
-        <v>-0.889</v>
+        <v>0.0565</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.9469</v>
+        <v>-0.4999</v>
       </c>
       <c r="U14" t="n">
-        <v>0.0579</v>
+        <v>0.5564</v>
       </c>
       <c r="V14" t="n">
         <v>-0.1952</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>2.4259</v>
+        <v>3.7104</v>
       </c>
       <c r="E15" t="n">
-        <v>4.5069</v>
+        <v>4.9539</v>
       </c>
       <c r="F15" t="n">
-        <v>-2.081</v>
+        <v>-1.2435</v>
       </c>
       <c r="G15" t="n">
         <v>3.9877</v>
@@ -1624,13 +1624,13 @@
         <v>1.5225</v>
       </c>
       <c r="S15" t="n">
-        <v>-2.492</v>
+        <v>-1.2074</v>
       </c>
       <c r="T15" t="n">
-        <v>-1.5634</v>
+        <v>-1.1164</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.9286</v>
+        <v>-0.091</v>
       </c>
       <c r="V15" t="n">
         <v>0.4952</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>1.429</v>
+        <v>2.0173</v>
       </c>
       <c r="E16" t="n">
-        <v>3.2997</v>
+        <v>3.5233</v>
       </c>
       <c r="F16" t="n">
-        <v>-1.8707</v>
+        <v>-1.5059</v>
       </c>
       <c r="G16" t="n">
         <v>1.2015</v>
@@ -1702,13 +1702,13 @@
         <v>1.305</v>
       </c>
       <c r="S16" t="n">
-        <v>-1.7897</v>
+        <v>-1.2014</v>
       </c>
       <c r="T16" t="n">
-        <v>-1.0274</v>
+        <v>-0.8038999999999999</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.7622</v>
+        <v>-0.3975</v>
       </c>
       <c r="V16" t="n">
         <v>1.7997</v>
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>1.131</v>
+        <v>0.0815</v>
       </c>
       <c r="E17" t="n">
-        <v>2.1142</v>
+        <v>0.8849</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.9832</v>
+        <v>-0.8034</v>
       </c>
       <c r="G17" t="n">
         <v>1.8972</v>
@@ -1780,13 +1780,13 @@
         <v>0.87</v>
       </c>
       <c r="S17" t="n">
-        <v>1.5792</v>
+        <v>0.5296</v>
       </c>
       <c r="T17" t="n">
-        <v>1.9047</v>
+        <v>0.6754</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.3255</v>
+        <v>-0.1457</v>
       </c>
       <c r="V17" t="n">
         <v>-3.2154</v>
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.08169999999999999</v>
+        <v>-0.3283</v>
       </c>
       <c r="E18" t="n">
-        <v>0.3097</v>
+        <v>-0.1373</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.3915</v>
+        <v>-0.191</v>
       </c>
       <c r="G18" t="n">
         <v>1.1682</v>
@@ -1858,13 +1858,13 @@
         <v>0.435</v>
       </c>
       <c r="S18" t="n">
-        <v>0.5326</v>
+        <v>0.286</v>
       </c>
       <c r="T18" t="n">
-        <v>0.0601</v>
+        <v>-0.3869</v>
       </c>
       <c r="U18" t="n">
-        <v>0.4725</v>
+        <v>0.6729000000000001</v>
       </c>
       <c r="V18" t="n">
         <v>-1.13</v>
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-1.4795</v>
+        <v>-1.2946</v>
       </c>
       <c r="E19" t="n">
         <v>0.0007</v>
       </c>
       <c r="F19" t="n">
-        <v>-1.4803</v>
+        <v>-1.2953</v>
       </c>
       <c r="G19" t="n">
         <v>-1.6421</v>
@@ -1936,13 +1936,13 @@
         <v>0.435</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.6422</v>
+        <v>-0.4572</v>
       </c>
       <c r="T19" t="n">
         <v>-0.6044</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.0377</v>
+        <v>0.1472</v>
       </c>
       <c r="V19" t="n">
         <v>0.3698</v>
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-2.592</v>
+        <v>-1.7698</v>
       </c>
       <c r="E20" t="n">
-        <v>-1.8797</v>
+        <v>-1.4327</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.7124</v>
+        <v>-0.3372</v>
       </c>
       <c r="G20" t="n">
         <v>0.09619999999999999</v>
@@ -2014,13 +2014,13 @@
         <v>1.305</v>
       </c>
       <c r="S20" t="n">
-        <v>-1.5108</v>
+        <v>-0.6886</v>
       </c>
       <c r="T20" t="n">
-        <v>-1.2209</v>
+        <v>-0.7739</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.2899</v>
+        <v>0.0853</v>
       </c>
       <c r="V20" t="n">
         <v>-1.395</v>
@@ -2035,7 +2035,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>N. GALETTE</t>
+          <t>T. MCFADDEN</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,73 +2047,73 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-2.8051</v>
+        <v>-2.2453</v>
       </c>
       <c r="E21" t="n">
-        <v>-1.6916</v>
+        <v>-2.2216</v>
       </c>
       <c r="F21" t="n">
-        <v>-1.1136</v>
+        <v>-0.0237</v>
       </c>
       <c r="G21" t="n">
-        <v>-2.36</v>
+        <v>2.2894</v>
       </c>
       <c r="H21" t="n">
-        <v>-1.3352</v>
+        <v>1.2072</v>
       </c>
       <c r="I21" t="n">
-        <v>-1.0248</v>
+        <v>1.0822</v>
       </c>
       <c r="J21" t="n">
-        <v>-0.5956</v>
+        <v>3.1199</v>
       </c>
       <c r="K21" t="n">
-        <v>-0.6538</v>
+        <v>1.2775</v>
       </c>
       <c r="L21" t="n">
-        <v>0.0582</v>
+        <v>1.8424</v>
       </c>
       <c r="M21" t="n">
-        <v>-1.7643</v>
+        <v>-0.8305</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.6814</v>
+        <v>-0.0703</v>
       </c>
       <c r="O21" t="n">
-        <v>-1.0829</v>
+        <v>-0.7602</v>
       </c>
       <c r="P21" t="n">
-        <v>-0.435</v>
+        <v>-3.0451</v>
       </c>
       <c r="Q21" t="n">
-        <v>-1.0875</v>
+        <v>-4.3501</v>
       </c>
       <c r="R21" t="n">
-        <v>0.6525</v>
+        <v>1.305</v>
       </c>
       <c r="S21" t="n">
-        <v>0.1851</v>
+        <v>-1.2245</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.008399999999999999</v>
+        <v>-0.9913999999999999</v>
       </c>
       <c r="U21" t="n">
-        <v>0.1935</v>
+        <v>-0.2331</v>
       </c>
       <c r="V21" t="n">
-        <v>-0.1952</v>
+        <v>-0.265</v>
       </c>
       <c r="W21" t="n">
         <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>-0.1952</v>
+        <v>-0.265</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>T. MCFADDEN</t>
+          <t>N. GALETTE</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,67 +2125,67 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-3.9563</v>
+        <v>-3.1032</v>
       </c>
       <c r="E22" t="n">
-        <v>-2.6687</v>
+        <v>-2.1386</v>
       </c>
       <c r="F22" t="n">
-        <v>-1.2876</v>
+        <v>-0.9646</v>
       </c>
       <c r="G22" t="n">
-        <v>2.2894</v>
+        <v>-2.36</v>
       </c>
       <c r="H22" t="n">
-        <v>1.2072</v>
+        <v>-1.3352</v>
       </c>
       <c r="I22" t="n">
-        <v>1.0822</v>
+        <v>-1.0248</v>
       </c>
       <c r="J22" t="n">
-        <v>3.1199</v>
+        <v>-0.5956</v>
       </c>
       <c r="K22" t="n">
-        <v>1.2775</v>
+        <v>-0.6538</v>
       </c>
       <c r="L22" t="n">
-        <v>1.8424</v>
+        <v>0.0582</v>
       </c>
       <c r="M22" t="n">
-        <v>-0.8305</v>
+        <v>-1.7643</v>
       </c>
       <c r="N22" t="n">
-        <v>-0.0703</v>
+        <v>-0.6814</v>
       </c>
       <c r="O22" t="n">
-        <v>-0.7602</v>
+        <v>-1.0829</v>
       </c>
       <c r="P22" t="n">
-        <v>-3.0451</v>
+        <v>-0.435</v>
       </c>
       <c r="Q22" t="n">
-        <v>-4.3501</v>
+        <v>-1.0875</v>
       </c>
       <c r="R22" t="n">
-        <v>1.305</v>
+        <v>0.6525</v>
       </c>
       <c r="S22" t="n">
-        <v>-2.9355</v>
+        <v>-0.113</v>
       </c>
       <c r="T22" t="n">
-        <v>-1.4384</v>
+        <v>-0.4554</v>
       </c>
       <c r="U22" t="n">
-        <v>-1.4971</v>
+        <v>0.3425</v>
       </c>
       <c r="V22" t="n">
-        <v>-0.265</v>
+        <v>-0.1952</v>
       </c>
       <c r="W22" t="n">
         <v>0</v>
       </c>
       <c r="X22" t="n">
-        <v>-0.265</v>
+        <v>-0.1952</v>
       </c>
     </row>
     <row r="23">
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-5.6193</v>
+        <v>-5.3894</v>
       </c>
       <c r="E23" t="n">
-        <v>-3.4557</v>
+        <v>-3.3439</v>
       </c>
       <c r="F23" t="n">
-        <v>-2.1637</v>
+        <v>-2.0455</v>
       </c>
       <c r="G23" t="n">
         <v>-3.3231</v>
@@ -2248,13 +2248,13 @@
         <v>0.2175</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.1011</v>
+        <v>0.1289</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.3425</v>
+        <v>-0.2307</v>
       </c>
       <c r="U23" t="n">
-        <v>0.2414</v>
+        <v>0.3596</v>
       </c>
       <c r="V23" t="n">
         <v>-1.3252</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-6.3096</v>
+        <v>-6.0116</v>
       </c>
       <c r="E24" t="n">
         <v>-2.2081</v>
       </c>
       <c r="F24" t="n">
-        <v>-4.1016</v>
+        <v>-3.8036</v>
       </c>
       <c r="G24" t="n">
         <v>-1.9925</v>
@@ -2326,13 +2326,13 @@
         <v>0.6525</v>
       </c>
       <c r="S24" t="n">
-        <v>-1.442</v>
+        <v>-1.144</v>
       </c>
       <c r="T24" t="n">
         <v>-0.9589</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.4831</v>
+        <v>-0.1851</v>
       </c>
       <c r="V24" t="n">
         <v>-0.265</v>
@@ -2359,13 +2359,13 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-14.3641</v>
+        <v>-9.893999999999998</v>
       </c>
       <c r="E25" t="n">
-        <v>0.6828000000000003</v>
+        <v>0.6830999999999992</v>
       </c>
       <c r="F25" t="n">
-        <v>-15.0475</v>
+        <v>-10.5771</v>
       </c>
       <c r="G25" t="n">
         <v>4.8127</v>
@@ -2404,16 +2404,16 @@
         <v>9.7875</v>
       </c>
       <c r="S25" t="n">
-        <v>-9.5054</v>
+        <v>-5.035100000000001</v>
       </c>
       <c r="T25" t="n">
         <v>-6.1464</v>
       </c>
       <c r="U25" t="n">
-        <v>-3.3588</v>
+        <v>1.1115</v>
       </c>
       <c r="V25" t="n">
-        <v>-5.3213</v>
+        <v>-5.321299999999999</v>
       </c>
       <c r="W25" t="n">
         <v>5.6705</v>
